--- a/nn_results.xlsx
+++ b/nn_results.xlsx
@@ -22,6 +22,7 @@
     <sheet name="ConstrainedGoToOpen_1c" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="ConstrainedOpenDoorLoc_2c" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="ConstrainedOpenDoorsOrder_2c" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="ConstrainedGoToOpen_2c" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -817,6 +818,62 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>720.14 ± 431.88</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>45.81 ± 153.72</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
